--- a/output/pdf_financials_xlsx/HCM.H.xlsx
+++ b/output/pdf_financials_xlsx/HCM.H.xlsx
@@ -2307,52 +2307,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.311447</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.235102</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009441</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.043196</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>604.936</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>272.04</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>128.353</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>213.322</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.213322</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>241.721</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>347.887</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>110.684</v>
+        <v>0.135975</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>20.456</v>
+        <v>0.026168</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.065372</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.007808</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.007575</v>
       </c>
     </row>
     <row r="35">
@@ -2417,52 +2417,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.311447</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.235102</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009441</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.043196</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>604.936</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>272.04</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>128.353</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>213.322</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.213322</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>241.721</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>347.887</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>110.684</v>
+        <v>0.135975</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>20.456</v>
+        <v>0.026168</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.065372</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.007808</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.007575</v>
       </c>
     </row>
     <row r="37">
@@ -3077,46 +3077,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.331374</v>
+        <v>0.019927</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.387092</v>
+        <v>0.15199</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.149024</v>
+        <v>0.139583</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.09256499999999999</v>
+        <v>0.049369</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>702.329</v>
+        <v>97.393</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>524.859</v>
+        <v>252.819</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>173.851</v>
+        <v>45.498</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>249.047</v>
+        <v>35.725</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.249047</v>
+        <v>0.035725</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>295.884</v>
+        <v>54.163</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>366.703</v>
+        <v>18.816</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0</v>
+        <v>0.08104</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0</v>
+        <v>0.036845</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.616586</v>
+        <v>1.551214</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -43654,7 +43654,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -46664,7 +46664,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -47390,7 +47390,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -48608,7 +48608,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">

--- a/output/pdf_financials_xlsx/HCM.H.xlsx
+++ b/output/pdf_financials_xlsx/HCM.H.xlsx
@@ -1538,11 +1538,15 @@
       <c r="M20" s="3" t="n">
         <v>-4899.259</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>-1.706944</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>43.464788</v>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P20" s="3" t="n">
         <v>-0.085926</v>
@@ -1594,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>-1.019608</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-0.91478</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -4049,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.536145</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.157199</v>
       </c>
       <c r="P64" s="3" t="n">
         <v>0.017027</v>
@@ -6591,25 +6595,25 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>25.026</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>136.189</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>372.266</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>490.531</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.455014</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>281.8</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>60.348</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -6637,43 +6641,43 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012736</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023892</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00077</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-8.276</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-1.07</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-3.303</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008166</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-5.001</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-4.868</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.879</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017013</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -7938,43 +7942,43 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012736</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023892</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00077</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-8.276</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-1.07</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-3.303</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008166</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-5.001</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-4.868</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.879</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017013</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -7993,43 +7997,43 @@
         <v>-1.003757</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.541069</v>
+        <v>-0.553805</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.972333</v>
+        <v>-0.996225</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.398344</v>
+        <v>-0.399114</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2448.398</v>
+        <v>-2456.674</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-3184.807</v>
+        <v>-3185.877</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-3788.136</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-2340.188</v>
+        <v>-2343.491</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.177503</v>
+        <v>-1.185669</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1408.363</v>
+        <v>-1413.364</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1850.804</v>
+        <v>-1855.672</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-1186.324</v>
+        <v>-1187.203</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-1.491726</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.461847</v>
+        <v>-1.47886</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.057564</v>
@@ -25084,7 +25088,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -27414,7 +27422,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -29032,7 +29044,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -33520,7 +33536,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -36084,7 +36104,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -45086,7 +45110,11 @@
           <t>Loss from discontinued operations 11,15</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
